--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.64502529624964</v>
+        <v>5.629816610640567</v>
       </c>
       <c r="D2" t="n">
-        <v>58.2804878118079</v>
+        <v>9.470579269418785</v>
       </c>
       <c r="E2" t="n">
-        <v>13.49313094763552</v>
+        <v>2.192633778990772</v>
       </c>
       <c r="F2" t="n">
-        <v>6.055083082343602</v>
+        <v>0.9839510008808352</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.37842318564782</v>
+        <v>7.211493767667771</v>
       </c>
       <c r="D3" t="n">
-        <v>53.46547097485493</v>
+        <v>8.688139033413927</v>
       </c>
       <c r="E3" t="n">
-        <v>13.49313094763552</v>
+        <v>2.192633778990772</v>
       </c>
       <c r="F3" t="n">
-        <v>6.055083082343602</v>
+        <v>0.9839510008808352</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.43368330486993</v>
+        <v>11.60797353704136</v>
       </c>
       <c r="D4" t="n">
-        <v>71.45801780041944</v>
+        <v>11.61192789256816</v>
       </c>
       <c r="E4" t="n">
-        <v>13.49313094763552</v>
+        <v>2.192633778990772</v>
       </c>
       <c r="F4" t="n">
-        <v>6.055083082343602</v>
+        <v>0.9839510008808352</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>64.35601945457421</v>
+        <v>10.45785316136831</v>
       </c>
       <c r="D5" t="n">
-        <v>64.1252838052667</v>
+        <v>10.42035861835584</v>
       </c>
       <c r="E5" t="n">
-        <v>13.49313094763552</v>
+        <v>2.192633778990772</v>
       </c>
       <c r="F5" t="n">
-        <v>6.055083082343602</v>
+        <v>0.9839510008808352</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.05789515942312</v>
+        <v>9.759407963406257</v>
       </c>
       <c r="D6" t="n">
-        <v>59.96525189260807</v>
+        <v>9.744353432548813</v>
       </c>
       <c r="E6" t="n">
-        <v>13.49313094763552</v>
+        <v>2.192633778990772</v>
       </c>
       <c r="F6" t="n">
-        <v>6.055083082343602</v>
+        <v>0.9839510008808352</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
